--- a/pl-automation/CTC_Conference_PL_Builder.xlsx
+++ b/pl-automation/CTC_Conference_PL_Builder.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="298">
   <si>
     <t xml:space="preserve">PROPOSAL SUMMARY</t>
   </si>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">PRE-PLANNING WORKLOAD</t>
   </si>
   <si>
-    <t xml:space="preserve">MARGIN CHECK</t>
+    <t xml:space="preserve">TRUE COST VIEW</t>
   </si>
   <si>
     <t xml:space="preserve">CATEGORY</t>
@@ -73,28 +73,25 @@
     <t xml:space="preserve">Managers</t>
   </si>
   <si>
-    <t xml:space="preserve">Target net margin</t>
+    <t xml:space="preserve">True cost of delivery</t>
   </si>
   <si>
     <t xml:space="preserve">Coordinators</t>
   </si>
   <si>
-    <t xml:space="preserve">This P&amp;L's net margin</t>
+    <t xml:space="preserve">True net profit</t>
   </si>
   <si>
     <t xml:space="preserve">Team (project management &amp; meetings)</t>
   </si>
   <si>
-    <t xml:space="preserve">Client price that hits target</t>
+    <t xml:space="preserve">True net margin</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL PRE-PLANNING</t>
   </si>
   <si>
-    <t xml:space="preserve">Gap vs grand total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRS / PERSON / WEEK above roughly 10 means the headcount is too thin for the scope. A positive margin gap means the client price is short of the target margin.</t>
+    <t xml:space="preserve">Client price for target margin</t>
   </si>
   <si>
     <t xml:space="preserve">EVENT MANAGEMENT</t>
@@ -341,6 +338,18 @@
   </si>
   <si>
     <t xml:space="preserve">Used by the margin check on the P&amp;L — what client price hits this margin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilization %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a paid hour that is billable to a client. 100% leaves the P&amp;L exactly as quoted; agencies plan around 75-85%. Measure it before trusting it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead % of direct labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent, software, insurance, non-billable salaries as a share of staff cost. Typical agency range 15-30%. Feeds the TRUE COST view only.</t>
   </si>
   <si>
     <t xml:space="preserve">8.  ONSITE ROLE TITLES</t>
@@ -900,6 +909,21 @@
   </si>
   <si>
     <t xml:space="preserve">•  MULTI-YEAR DISCOUNT = the 5% off additional years. Off by default — switch it on at the bottom of INPUTS section 7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE TRUE COST VIEW  —  read this before trusting a margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  The % Profit column is a GROSS margin on direct labour. It counts salary and burden. It does not count the part of the year staff are paid but not billable, and it does not count real overhead. Those are the two inputs at the bottom of INPUTS section 7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  UTILIZATION % = billable hours divided by paid hours. At 100% the true cost view matches the quoted cost exactly, so the workbook behaves as before until you change it. Agencies plan around 75-85%. Measure it from timesheets against payroll before you trust any number here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  OVERHEAD % OF DIRECT LABOR = rent, software, insurance, non-billable salaries and business development as a share of staff cost. Typical agency range is 15-30%. This supersedes the $0.61/hr line, which is around 1% of a manager hour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  TRUE NET MARGIN on the P&amp;L is what is left after both. At 80% utilization and 15% overhead a P&amp;L quoting 36% returns about 8%. CLIENT PRICE FOR TARGET MARGIN tells you what to charge instead.</t>
   </si>
 </sst>
 </file>
@@ -1237,6 +1261,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1254,14 +1286,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1915,9 +1939,9 @@
         <v>16</v>
       </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="7" t="n">
-        <f aca="false">INPUTS!$C$52</f>
-        <v>0.4</v>
+      <c r="J16" s="6" t="n">
+        <f aca="false">(D6+D7)/INPUTS!$C$53*(1+INPUTS!$C$54)+D8</f>
+        <v>45063.12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1948,9 +1972,9 @@
         <v>18</v>
       </c>
       <c r="I17" s="5"/>
-      <c r="J17" s="7" t="n">
-        <f aca="false">F12</f>
-        <v>0.359252655376872</v>
+      <c r="J17" s="6" t="n">
+        <f aca="false">C12-((D6+D7)/INPUTS!$C$53*(1+INPUTS!$C$54)+D8)</f>
+        <v>25265.88</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,53 +2001,54 @@
         <f aca="false">IF(OR(F18=0,INPUTS!$C$23=0),"",C18/F18/INPUTS!$C$23)</f>
         <v>1.6025641025641</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="6" t="n">
-        <f aca="false">IF(INPUTS!$C$52&gt;=1,"",D12/(1-INPUTS!$C$52))</f>
-        <v>75105.2</v>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19" t="n">
+        <f aca="false">IF(C12=0,"",(C12-((D6+D7)/INPUTS!$C$53*(1+INPUTS!$C$54)+D8))/C12)</f>
+        <v>0.359252655376872</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="21" t="n">
         <f aca="false">SUM(C16:C18)</f>
         <v>568</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="22" t="n">
         <f aca="false">IF(C19=0,"",E19/C19)</f>
         <v>56.7676056338028</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="23" t="n">
         <f aca="false">SUM(E16:E18)</f>
         <v>32244</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="21" t="n">
         <f aca="false">INPUTS!$C$29+INPUTS!$C$30</f>
         <v>2</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="23" t="s">
+      <c r="G19" s="24"/>
+      <c r="H19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24" t="n">
-        <f aca="false">IF(INPUTS!$C$52&gt;=1,"",D12/(1-INPUTS!$C$52)-C12)</f>
-        <v>4776.20000000001</v>
+      <c r="I19" s="5"/>
+      <c r="J19" s="6" t="n">
+        <f aca="false">IF(INPUTS!$C$52&gt;=1,"",((D6+D7)/INPUTS!$C$53*(1+INPUTS!$C$54)+D8)/(1-INPUTS!$C$52))</f>
+        <v>75105.2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="25" t="s">
-        <v>23</v>
+      <c r="B20" s="25" t="str">
+        <f aca="false">"HRS / PERSON / WEEK above ~10 means the headcount is too thin for the scope.    TRUE COST assumes "&amp;TEXT(INPUTS!$C$53,"0%")&amp;" utilization and "&amp;TEXT(INPUTS!$C$54,"0%")&amp;" overhead — at 100% and 0% it equals the quoted cost above."</f>
+        <v>HRS / PERSON / WEEK above ~10 means the headcount is too thin for the scope.    TRUE COST assumes 100% utilization and 0% overhead — at 100% and 0% it equals the quoted cost above.</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -2036,10 +2061,10 @@
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>11</v>
@@ -2048,7 +2073,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>11</v>
@@ -2937,7 +2962,7 @@
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -2950,10 +2975,10 @@
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>11</v>
@@ -2962,7 +2987,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>11</v>
@@ -2983,7 +3008,7 @@
         <v>PM</v>
       </c>
       <c r="B47" s="27" t="str">
-        <f aca="false">IF(1&lt;=INPUTS!$C$27,INPUTS!$C$56,"")</f>
+        <f aca="false">IF(1&lt;=INPUTS!$C$27,INPUTS!$C$58,"")</f>
         <v>Project Manager</v>
       </c>
       <c r="C47" s="28" t="n">
@@ -3025,7 +3050,7 @@
         <v>PM</v>
       </c>
       <c r="B48" s="27" t="str">
-        <f aca="false">IF(2&lt;=INPUTS!$C$27,INPUTS!$C$57,"")</f>
+        <f aca="false">IF(2&lt;=INPUTS!$C$27,INPUTS!$C$59,"")</f>
         <v>Event Manager</v>
       </c>
       <c r="C48" s="28" t="n">
@@ -3067,7 +3092,7 @@
         <v>PM</v>
       </c>
       <c r="B49" s="27" t="str">
-        <f aca="false">IF(3&lt;=INPUTS!$C$27,INPUTS!$C$58,"")</f>
+        <f aca="false">IF(3&lt;=INPUTS!$C$27,INPUTS!$C$60,"")</f>
         <v>Executive Producer</v>
       </c>
       <c r="C49" s="28" t="n">
@@ -3109,7 +3134,7 @@
         <v/>
       </c>
       <c r="B50" s="27" t="str">
-        <f aca="false">IF(4&lt;=INPUTS!$C$27,INPUTS!$C$59,"")</f>
+        <f aca="false">IF(4&lt;=INPUTS!$C$27,INPUTS!$C$61,"")</f>
         <v/>
       </c>
       <c r="C50" s="28" t="str">
@@ -3151,7 +3176,7 @@
         <v/>
       </c>
       <c r="B51" s="27" t="str">
-        <f aca="false">IF(5&lt;=INPUTS!$C$27,INPUTS!$C$60,"")</f>
+        <f aca="false">IF(5&lt;=INPUTS!$C$27,INPUTS!$C$62,"")</f>
         <v/>
       </c>
       <c r="C51" s="28" t="str">
@@ -3193,7 +3218,7 @@
         <v/>
       </c>
       <c r="B52" s="27" t="str">
-        <f aca="false">IF(6&lt;=INPUTS!$C$27,INPUTS!$C$61,"")</f>
+        <f aca="false">IF(6&lt;=INPUTS!$C$27,INPUTS!$C$63,"")</f>
         <v/>
       </c>
       <c r="C52" s="28" t="str">
@@ -3235,7 +3260,7 @@
         <v/>
       </c>
       <c r="B53" s="27" t="str">
-        <f aca="false">IF(7&lt;=INPUTS!$C$27,INPUTS!$C$62,"")</f>
+        <f aca="false">IF(7&lt;=INPUTS!$C$27,INPUTS!$C$64,"")</f>
         <v/>
       </c>
       <c r="C53" s="28" t="str">
@@ -3277,7 +3302,7 @@
         <v/>
       </c>
       <c r="B54" s="27" t="str">
-        <f aca="false">IF(8&lt;=INPUTS!$C$27,INPUTS!$C$63,"")</f>
+        <f aca="false">IF(8&lt;=INPUTS!$C$27,INPUTS!$C$65,"")</f>
         <v/>
       </c>
       <c r="C54" s="28" t="str">
@@ -3319,7 +3344,7 @@
         <v>EC</v>
       </c>
       <c r="B55" s="27" t="str">
-        <f aca="false">IF(1&lt;=INPUTS!$C$28,INPUTS!$C$67,"")</f>
+        <f aca="false">IF(1&lt;=INPUTS!$C$28,INPUTS!$C$69,"")</f>
         <v>Event Coordinator</v>
       </c>
       <c r="C55" s="28" t="n">
@@ -3361,7 +3386,7 @@
         <v>EC</v>
       </c>
       <c r="B56" s="27" t="str">
-        <f aca="false">IF(2&lt;=INPUTS!$C$28,INPUTS!$C$68,"")</f>
+        <f aca="false">IF(2&lt;=INPUTS!$C$28,INPUTS!$C$70,"")</f>
         <v>Registration Coordinator</v>
       </c>
       <c r="C56" s="28" t="n">
@@ -3403,7 +3428,7 @@
         <v/>
       </c>
       <c r="B57" s="27" t="str">
-        <f aca="false">IF(3&lt;=INPUTS!$C$28,INPUTS!$C$69,"")</f>
+        <f aca="false">IF(3&lt;=INPUTS!$C$28,INPUTS!$C$71,"")</f>
         <v/>
       </c>
       <c r="C57" s="28" t="str">
@@ -3445,7 +3470,7 @@
         <v/>
       </c>
       <c r="B58" s="27" t="str">
-        <f aca="false">IF(4&lt;=INPUTS!$C$28,INPUTS!$C$70,"")</f>
+        <f aca="false">IF(4&lt;=INPUTS!$C$28,INPUTS!$C$72,"")</f>
         <v/>
       </c>
       <c r="C58" s="28" t="str">
@@ -3487,7 +3512,7 @@
         <v/>
       </c>
       <c r="B59" s="27" t="str">
-        <f aca="false">IF(5&lt;=INPUTS!$C$28,INPUTS!$C$71,"")</f>
+        <f aca="false">IF(5&lt;=INPUTS!$C$28,INPUTS!$C$73,"")</f>
         <v/>
       </c>
       <c r="C59" s="28" t="str">
@@ -3529,7 +3554,7 @@
         <v/>
       </c>
       <c r="B60" s="27" t="str">
-        <f aca="false">IF(6&lt;=INPUTS!$C$28,INPUTS!$C$72,"")</f>
+        <f aca="false">IF(6&lt;=INPUTS!$C$28,INPUTS!$C$74,"")</f>
         <v/>
       </c>
       <c r="C60" s="28" t="str">
@@ -3571,7 +3596,7 @@
         <v/>
       </c>
       <c r="B61" s="27" t="str">
-        <f aca="false">IF(7&lt;=INPUTS!$C$28,INPUTS!$C$73,"")</f>
+        <f aca="false">IF(7&lt;=INPUTS!$C$28,INPUTS!$C$75,"")</f>
         <v/>
       </c>
       <c r="C61" s="28" t="str">
@@ -3613,7 +3638,7 @@
         <v/>
       </c>
       <c r="B62" s="27" t="str">
-        <f aca="false">IF(8&lt;=INPUTS!$C$28,INPUTS!$C$74,"")</f>
+        <f aca="false">IF(8&lt;=INPUTS!$C$28,INPUTS!$C$76,"")</f>
         <v/>
       </c>
       <c r="C62" s="28" t="str">
@@ -3731,7 +3756,7 @@
     </row>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
@@ -3742,18 +3767,18 @@
         <v>1</v>
       </c>
       <c r="C68" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="E68" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" s="15" t="n">
         <f aca="false">D43</f>
@@ -3770,7 +3795,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C70" s="15" t="n">
         <f aca="false">D64</f>
@@ -3786,22 +3811,22 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C71" s="19" t="n">
+      <c r="B71" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" s="21" t="n">
         <f aca="false">SUM(C69:C70)</f>
         <v>792</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="21" t="n">
+      <c r="D71" s="22"/>
+      <c r="E71" s="23" t="n">
         <f aca="false">SUM(E69:E70)</f>
         <v>483.12</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -3830,7 +3855,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:D76"/>
+  <dimension ref="B1:D78"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.6"/>
@@ -3841,130 +3866,130 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="40" t="s">
         <v>40</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="40" t="s">
         <v>42</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="40" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" s="41" t="n">
         <v>500</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="41" t="n">
         <v>60</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="41" t="n">
         <v>20</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="41" t="n">
         <v>15</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="41" t="n">
         <v>5</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="41" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="41" t="n">
         <v>3</v>
@@ -3972,7 +3997,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="41" t="n">
         <v>1</v>
@@ -3980,7 +4005,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="41" t="n">
         <v>0</v>
@@ -3988,7 +4013,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="43" t="n">
         <f aca="false">C18+C19+C20</f>
@@ -3997,60 +4022,60 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="41" t="n">
         <v>9</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" s="43" t="n">
         <f aca="false">ROUND(C22*4.33,0)</f>
         <v>39</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C24" s="44" t="n">
         <f aca="false">ROUND((MAX(1,C10)/250)^(1/3)*(MAX(1,C22)/6)^(1/2)*(MAX(1,C18)/3)^(1/4),2)</f>
         <v>1.54</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27" s="41" t="n">
         <v>3</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" s="41" t="n">
         <v>2</v>
@@ -4058,18 +4083,18 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C29" s="41" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C30" s="41" t="n">
         <v>1</v>
@@ -4077,36 +4102,36 @@
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="45" t="n">
         <v>60</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C34" s="45" t="n">
         <v>42</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C35" s="45" t="n">
         <v>90</v>
@@ -4114,7 +4139,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" s="45" t="n">
         <v>65</v>
@@ -4122,7 +4147,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="45" t="n">
         <v>100</v>
@@ -4130,7 +4155,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C38" s="45" t="n">
         <v>65</v>
@@ -4138,47 +4163,47 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C39" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C42" s="41" t="n">
         <v>12</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C43" s="41" t="n">
         <v>8</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" s="41" t="n">
         <v>2</v>
@@ -4186,7 +4211,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C45" s="41" t="n">
         <v>8</v>
@@ -4194,160 +4219,169 @@
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C48" s="45" t="n">
         <v>0.61</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C49" s="47" t="n">
         <v>0.02</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50" s="47" t="n">
         <v>0.05</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="40" t="s">
         <v>102</v>
-      </c>
-      <c r="C51" s="40" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C52" s="47" t="n">
         <v>0.4</v>
       </c>
       <c r="D52" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="42" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="3" t="s">
+      <c r="C53" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="42" t="s">
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="C54" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="25" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="39" t="s">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="40" t="s">
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="42" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="39" t="s">
+      <c r="D57" s="25" t="s">
         <v>111</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="40" t="s">
         <v>113</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" s="40" t="s">
         <v>115</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="40" t="s">
         <v>117</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="40" t="s">
         <v>119</v>
-      </c>
-      <c r="C61" s="40" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" s="40" t="s">
         <v>121</v>
-      </c>
-      <c r="C62" s="40" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="40" t="s">
         <v>123</v>
-      </c>
-      <c r="C63" s="40" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="40" t="s">
         <v>125</v>
-      </c>
-      <c r="C64" s="40" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C65" s="40" t="s">
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="39" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="42" t="s">
+      <c r="C66" s="40" t="s">
         <v>129</v>
       </c>
     </row>
@@ -4360,75 +4394,88 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="39" t="s">
+      <c r="B68" s="42" t="s">
         <v>132</v>
-      </c>
-      <c r="C68" s="40" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="40" t="s">
         <v>134</v>
-      </c>
-      <c r="C69" s="40" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C70" s="40" t="s">
         <v>136</v>
-      </c>
-      <c r="C70" s="40" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C71" s="40" t="s">
         <v>138</v>
-      </c>
-      <c r="C71" s="40" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C72" s="40" t="s">
         <v>140</v>
-      </c>
-      <c r="C72" s="40" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="40" t="s">
         <v>142</v>
-      </c>
-      <c r="C73" s="40" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="C74" s="40" t="s">
         <v>144</v>
-      </c>
-      <c r="C74" s="40" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" s="40" t="s">
         <v>146</v>
-      </c>
-      <c r="C75" s="40" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C76" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="C76" s="40" t="s">
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="39" t="s">
         <v>149</v>
+      </c>
+      <c r="C77" s="40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C78" s="40" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -4478,7 +4525,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4495,51 +4542,51 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O3" s="48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P3" s="48" t="s">
         <v>11</v>
@@ -4551,7 +4598,7 @@
         <v>3</v>
       </c>
       <c r="S3" s="48" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="T3" s="48" t="s">
         <v>13</v>
@@ -4560,7 +4607,7 @@
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="49"/>
       <c r="B4" s="49" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4574,7 +4621,7 @@
       <c r="L4" s="49"/>
       <c r="M4" s="49"/>
       <c r="O4" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="P4" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O4,$D$4:$D$76,"Yes")</f>
@@ -4602,16 +4649,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F5" s="15" t="n">
         <f aca="false">3*INPUTS!$C$23+ROUND(5*INPUTS!$C$24,0)</f>
@@ -4639,10 +4686,10 @@
         <v>8436</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="P5" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O5,$D$4:$D$76,"Yes")</f>
@@ -4668,7 +4715,7 @@
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="49"/>
       <c r="B6" s="49" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="49"/>
@@ -4682,7 +4729,7 @@
       <c r="L6" s="49"/>
       <c r="M6" s="49"/>
       <c r="O6" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="P6" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O6,$D$4:$D$76,"Yes")</f>
@@ -4710,16 +4757,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">ROUND(6*INPUTS!$C$24,0)</f>
@@ -4747,10 +4794,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="P7" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O7,$D$4:$D$76,"Yes")</f>
@@ -4778,16 +4825,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="D8" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F8" s="15" t="n">
         <f aca="false">ROUND(6*INPUTS!$C$24,0)</f>
@@ -4815,10 +4862,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P8" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O8,$D$4:$D$76,"Yes")</f>
@@ -4846,16 +4893,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">ROUND(10*INPUTS!$C$15,0)</f>
@@ -4883,10 +4930,10 @@
         <v>0</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P9" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O9,$D$4:$D$76,"Yes")</f>
@@ -4914,16 +4961,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F10" s="15" t="n">
         <f aca="false">ROUND(5*INPUTS!$C$24,0)</f>
@@ -4951,10 +4998,10 @@
         <v>0</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="P10" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O10,$D$4:$D$76,"Yes")</f>
@@ -4980,7 +5027,7 @@
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="49"/>
       <c r="B11" s="49" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="49"/>
@@ -4994,7 +5041,7 @@
       <c r="L11" s="49"/>
       <c r="M11" s="49"/>
       <c r="O11" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="P11" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O11,$D$4:$D$76,"Yes")</f>
@@ -5022,16 +5069,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F12" s="15" t="n">
         <f aca="false">ROUND(16*INPUTS!$C$24,0)</f>
@@ -5059,10 +5106,10 @@
         <v>1500</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P12" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O12,$D$4:$D$76,"Yes")</f>
@@ -5090,16 +5137,16 @@
         <v>7</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F13" s="15" t="n">
         <f aca="false">ROUND(10*INPUTS!$C$24,0)</f>
@@ -5127,10 +5174,10 @@
         <v>900</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P13" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O13,$D$4:$D$76,"Yes")</f>
@@ -5156,7 +5203,7 @@
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="49"/>
       <c r="B14" s="49" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="49"/>
@@ -5170,7 +5217,7 @@
       <c r="L14" s="49"/>
       <c r="M14" s="49"/>
       <c r="O14" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P14" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O14,$D$4:$D$76,"Yes")</f>
@@ -5198,16 +5245,16 @@
         <v>8</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F15" s="15" t="n">
         <f aca="false">ROUND(7*INPUTS!$C$24,0)</f>
@@ -5235,10 +5282,10 @@
         <v>660</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="P15" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O15,$D$4:$D$76,"Yes")</f>
@@ -5266,16 +5313,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F16" s="15" t="n">
         <f aca="false">ROUND(14*INPUTS!$C$24,0)</f>
@@ -5303,10 +5350,10 @@
         <v>1320</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="P16" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O16,$D$4:$D$76,"Yes")</f>
@@ -5334,16 +5381,16 @@
         <v>10</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -5371,10 +5418,10 @@
         <v>720</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P17" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O17,$D$4:$D$76,"Yes")</f>
@@ -5402,16 +5449,16 @@
         <v>11</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F18" s="15" t="n">
         <f aca="false">ROUND(26*INPUTS!$C$24,0)</f>
@@ -5439,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P18" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O18,$D$4:$D$76,"Yes")</f>
@@ -5468,7 +5515,7 @@
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="49"/>
       <c r="B19" s="49" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C19" s="49"/>
       <c r="D19" s="49"/>
@@ -5482,7 +5529,7 @@
       <c r="L19" s="49"/>
       <c r="M19" s="49"/>
       <c r="O19" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P19" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O19,$D$4:$D$76,"Yes")</f>
@@ -5510,16 +5557,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F20" s="15" t="n">
         <f aca="false">ROUND(22*INPUTS!$C$24,0)</f>
@@ -5547,10 +5594,10 @@
         <v>2040</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P20" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O20,$D$4:$D$76,"Yes")</f>
@@ -5576,7 +5623,7 @@
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="49"/>
       <c r="B21" s="49" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -5590,7 +5637,7 @@
       <c r="L21" s="49"/>
       <c r="M21" s="49"/>
       <c r="O21" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P21" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O21,$D$4:$D$76,"Yes")</f>
@@ -5618,16 +5665,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F22" s="15" t="n">
         <f aca="false">ROUND(35*INPUTS!$C$24,0)</f>
@@ -5655,10 +5702,10 @@
         <v>2268</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P22" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O22,$D$4:$D$76,"Yes")</f>
@@ -5686,16 +5733,16 @@
         <v>14</v>
       </c>
       <c r="B23" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>208</v>
-      </c>
       <c r="D23" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F23" s="15" t="n">
         <f aca="false">ROUND(18*INPUTS!$C$24,0)</f>
@@ -5723,10 +5770,10 @@
         <v>1176</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P23" s="15" t="n">
         <f aca="false">SUMIFS($H$4:$H$76,$M$4:$M$76,$O23,$D$4:$D$76,"Yes")</f>
@@ -5754,16 +5801,16 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F24" s="15" t="n">
         <f aca="false">ROUND(25*INPUTS!$C$24,0)</f>
@@ -5791,13 +5838,13 @@
         <v>0</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="49"/>
       <c r="B25" s="49" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C25" s="49"/>
       <c r="D25" s="49"/>
@@ -5816,16 +5863,16 @@
         <v>16</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F26" s="15" t="n">
         <f aca="false">ROUND(20*INPUTS!$C$24,0)</f>
@@ -5853,13 +5900,13 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="49"/>
       <c r="B27" s="49" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C27" s="49"/>
       <c r="D27" s="49"/>
@@ -5878,16 +5925,16 @@
         <v>17</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F28" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -5915,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5923,16 +5970,16 @@
         <v>18</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F29" s="15" t="n">
         <f aca="false">ROUND(4*INPUTS!$C$24,0)</f>
@@ -5960,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5968,16 +6015,16 @@
         <v>19</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F30" s="15" t="n">
         <f aca="false">ROUND(3*INPUTS!$C$24,0)</f>
@@ -6005,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6013,16 +6060,16 @@
         <v>20</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F31" s="15" t="n">
         <f aca="false">ROUND(5*INPUTS!$C$24,0)</f>
@@ -6050,7 +6097,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6058,16 +6105,16 @@
         <v>21</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D32" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F32" s="15" t="n">
         <f aca="false">ROUND(3*INPUTS!$C$24,0)</f>
@@ -6095,13 +6142,13 @@
         <v>0</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="49"/>
       <c r="B33" s="49" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C33" s="49"/>
       <c r="D33" s="49"/>
@@ -6120,16 +6167,16 @@
         <v>22</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D34" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F34" s="15" t="n">
         <f aca="false">ROUND(5*INPUTS!$C$14,0)</f>
@@ -6157,7 +6204,7 @@
         <v>1050</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6165,16 +6212,16 @@
         <v>23</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D35" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F35" s="15" t="n">
         <f aca="false">ROUND(10*INPUTS!$C$24,0)</f>
@@ -6202,13 +6249,13 @@
         <v>630</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="49"/>
       <c r="B36" s="49" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C36" s="49"/>
       <c r="D36" s="49"/>
@@ -6227,16 +6274,16 @@
         <v>24</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D37" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F37" s="15" t="n">
         <f aca="false">ROUND(5*INPUTS!$C$24,0)</f>
@@ -6264,7 +6311,7 @@
         <v>480</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6272,16 +6319,16 @@
         <v>25</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D38" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F38" s="15" t="n">
         <f aca="false">ROUND(4*INPUTS!$C$24,0)</f>
@@ -6309,13 +6356,13 @@
         <v>360</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="49"/>
       <c r="B39" s="49" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C39" s="49"/>
       <c r="D39" s="49"/>
@@ -6334,16 +6381,16 @@
         <v>26</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D40" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F40" s="15" t="n">
         <f aca="false">ROUND(12*INPUTS!$C$24,0)</f>
@@ -6371,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6379,16 +6426,16 @@
         <v>27</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D41" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F41" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -6416,13 +6463,13 @@
         <v>0</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="49"/>
       <c r="B42" s="49" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C42" s="49"/>
       <c r="D42" s="49"/>
@@ -6441,16 +6488,16 @@
         <v>28</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D43" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F43" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -6478,7 +6525,7 @@
         <v>504</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6486,16 +6533,16 @@
         <v>29</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D44" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F44" s="15" t="n">
         <f aca="false">ROUND(1*INPUTS!$C$12,0)</f>
@@ -6523,13 +6570,13 @@
         <v>840</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="49"/>
       <c r="B45" s="49" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C45" s="49"/>
       <c r="D45" s="49"/>
@@ -6548,16 +6595,16 @@
         <v>30</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D46" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F46" s="15" t="n">
         <f aca="false">ROUND(0.7*INPUTS!$C$13,0)</f>
@@ -6585,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6593,16 +6640,16 @@
         <v>31</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D47" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F47" s="15" t="n">
         <f aca="false">ROUND(0.3*INPUTS!$C$13,0)</f>
@@ -6630,13 +6677,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="49"/>
       <c r="B48" s="49" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C48" s="49"/>
       <c r="D48" s="49"/>
@@ -6655,16 +6702,16 @@
         <v>32</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D49" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F49" s="15" t="n">
         <f aca="false">ROUND(18*INPUTS!$C$24,0)</f>
@@ -6692,7 +6739,7 @@
         <v>1680</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6700,16 +6747,16 @@
         <v>33</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D50" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F50" s="15" t="n">
         <f aca="false">ROUND(15*INPUTS!$C$24,0)</f>
@@ -6737,7 +6784,7 @@
         <v>1380</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6745,16 +6792,16 @@
         <v>34</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D51" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F51" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -6782,7 +6829,7 @@
         <v>720</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6790,16 +6837,16 @@
         <v>35</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F52" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -6827,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6835,16 +6882,16 @@
         <v>36</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D53" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F53" s="15" t="n">
         <f aca="false">ROUND(10*INPUTS!$C$24,0)</f>
@@ -6872,13 +6919,13 @@
         <v>0</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="49"/>
       <c r="B54" s="49" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C54" s="49"/>
       <c r="D54" s="49"/>
@@ -6897,16 +6944,16 @@
         <v>37</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D55" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F55" s="15" t="n">
         <f aca="false">ROUND(3*INPUTS!$C$24,0)</f>
@@ -6934,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6942,16 +6989,16 @@
         <v>38</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D56" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F56" s="15" t="n">
         <f aca="false">ROUND(4*INPUTS!$C$24,0)</f>
@@ -6979,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6987,16 +7034,16 @@
         <v>39</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D57" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F57" s="15" t="n">
         <f aca="false">ROUND(4*INPUTS!$C$24,0)</f>
@@ -7024,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7032,16 +7079,16 @@
         <v>40</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D58" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E58" s="27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F58" s="15" t="n">
         <f aca="false">ROUND(3*INPUTS!$C$24,0)</f>
@@ -7069,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7077,16 +7124,16 @@
         <v>41</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D59" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F59" s="15" t="n">
         <f aca="false">ROUND(3*INPUTS!$C$24,0)</f>
@@ -7114,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7122,16 +7169,16 @@
         <v>42</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D60" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E60" s="27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F60" s="15" t="n">
         <f aca="false">ROUND(3*INPUTS!$C$24,0)</f>
@@ -7159,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7167,16 +7214,16 @@
         <v>43</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D61" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F61" s="15" t="n">
         <f aca="false">ROUND(2*INPUTS!$C$24,0)</f>
@@ -7204,13 +7251,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="49"/>
       <c r="B62" s="49" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C62" s="49"/>
       <c r="D62" s="49"/>
@@ -7229,16 +7276,16 @@
         <v>44</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D63" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E63" s="27" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F63" s="15" t="n">
         <f aca="false">ROUND(12*INPUTS!$C$24,0)</f>
@@ -7266,13 +7313,13 @@
         <v>1080</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="49"/>
       <c r="B64" s="49" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C64" s="49"/>
       <c r="D64" s="49"/>
@@ -7291,16 +7338,16 @@
         <v>45</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D65" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F65" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -7328,7 +7375,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7336,16 +7383,16 @@
         <v>46</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D66" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F66" s="15" t="n">
         <f aca="false">ROUND(9*INPUTS!$C$24,0)</f>
@@ -7373,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7381,16 +7428,16 @@
         <v>47</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D67" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F67" s="15" t="n">
         <f aca="false">ROUND(5*INPUTS!$C$24,0)</f>
@@ -7418,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7426,16 +7473,16 @@
         <v>48</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D68" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E68" s="27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F68" s="15" t="n">
         <f aca="false">ROUND(5*INPUTS!$C$24,0)</f>
@@ -7463,13 +7510,13 @@
         <v>0</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="49"/>
       <c r="B69" s="49" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C69" s="49"/>
       <c r="D69" s="49"/>
@@ -7488,16 +7535,16 @@
         <v>49</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D70" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E70" s="27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F70" s="15" t="n">
         <f aca="false">ROUND(1*INPUTS!$C$11,0)</f>
@@ -7525,13 +7572,13 @@
         <v>3600</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="49"/>
       <c r="B71" s="49" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C71" s="49"/>
       <c r="D71" s="49"/>
@@ -7550,16 +7597,16 @@
         <v>50</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D72" s="52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E72" s="27" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F72" s="15" t="n">
         <f aca="false">ROUND(10*INPUTS!$C$24,0)</f>
@@ -7587,13 +7634,13 @@
         <v>900</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="49"/>
       <c r="B73" s="49" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C73" s="49"/>
       <c r="D73" s="49"/>
@@ -7612,16 +7659,16 @@
         <v>51</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D74" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F74" s="15" t="n">
         <f aca="false">ROUND(7*INPUTS!$C$24,0)</f>
@@ -7649,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7657,16 +7704,16 @@
         <v>52</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D75" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F75" s="15" t="n">
         <f aca="false">ROUND(8*INPUTS!$C$24,0)</f>
@@ -7694,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7702,16 +7749,16 @@
         <v>53</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D76" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E76" s="27" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F76" s="15" t="n">
         <f aca="false">ROUND(7*INPUTS!$C$24,0)</f>
@@ -7739,34 +7786,34 @@
         <v>0</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="18"/>
-      <c r="B77" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="19" t="n">
+      <c r="A77" s="20"/>
+      <c r="B77" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="21" t="n">
         <f aca="false">SUMIF($D$4:$D$76,"Yes",$H$4:$H$76)</f>
         <v>568</v>
       </c>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="21" t="n">
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="23" t="n">
         <f aca="false">SUMIF($D$4:$D$76,"Yes",$K$4:$K$76)</f>
         <v>48830</v>
       </c>
-      <c r="L77" s="21" t="n">
+      <c r="L77" s="23" t="n">
         <f aca="false">SUMIF($D$4:$D$76,"Yes",$L$4:$L$76)</f>
         <v>32244</v>
       </c>
-      <c r="M77" s="18"/>
+      <c r="M77" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7790,7 +7837,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:B28"/>
+  <dimension ref="B1:B34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -7799,117 +7846,142 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="53" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="53" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="53" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="53" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="53" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="53" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="53" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="53" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="53" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="53" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="53" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="53" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="53" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="53" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="53" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="53" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="53" t="s">
-        <v>289</v>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="53" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="53" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="53" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="53" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
